--- a/data/trans_camb/IP18_E_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18_E_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 11,83</t>
+          <t>-4,13; 12,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 3,95</t>
+          <t>-16,42; 3,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 7,04</t>
+          <t>-29,45; 8,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 22,02</t>
+          <t>3,79; 22,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 16,08</t>
+          <t>-3,73; 16,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 18,4</t>
+          <t>-10,98; 17,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 14,55</t>
+          <t>1,46; 13,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 7,22</t>
+          <t>-7,2; 6,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 10,37</t>
+          <t>-12,11; 10,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 14,02</t>
+          <t>-4,4; 14,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 4,59</t>
+          <t>-17,86; 3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 7,84</t>
+          <t>-32,07; 9,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 28,97</t>
+          <t>3,87; 29,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 20,9</t>
+          <t>-4,27; 20,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 23,16</t>
+          <t>-11,15; 22,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 17,54</t>
+          <t>1,72; 16,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 8,69</t>
+          <t>-7,96; 8,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 12,36</t>
+          <t>-12,94; 12,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 0,46</t>
+          <t>-9,57; 0,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,64</t>
+          <t>-4,18; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 2,64</t>
+          <t>-23,65; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 8,65</t>
+          <t>-5,42; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,03</t>
+          <t>3,54; 14,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,61</t>
+          <t>5,74; 15,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,6</t>
+          <t>-5,48; 3,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,6</t>
+          <t>0,84; 7,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 6,87</t>
+          <t>-6,53; 7,04</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,32</t>
+          <t>-9,77; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,88</t>
+          <t>-4,31; 3,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 2,75</t>
+          <t>-24,46; 2,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 9,94</t>
+          <t>-5,79; 9,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 17,84</t>
+          <t>3,73; 16,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 18,49</t>
+          <t>6,09; 19,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,96</t>
+          <t>-5,68; 3,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,54</t>
+          <t>0,89; 8,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 7,48</t>
+          <t>-6,63; 7,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 5,89</t>
+          <t>-7,84; 6,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 6,22</t>
+          <t>-7,21; 6,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,19; -3,63</t>
+          <t>-38,37; -2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 3,66</t>
+          <t>-7,16; 4,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 1,21</t>
+          <t>-12,47; 1,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,29</t>
+          <t>0,92; 8,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,38</t>
+          <t>-5,7; 3,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 2,03</t>
+          <t>-7,69; 1,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 0,73</t>
+          <t>-19,08; 0,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 6,41</t>
+          <t>-8,15; 6,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 6,81</t>
+          <t>-7,45; 6,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -3,85</t>
+          <t>-40,14; -2,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 3,84</t>
+          <t>-7,26; 4,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 1,27</t>
+          <t>-12,76; 1,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,24</t>
+          <t>0,93; 9,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 3,61</t>
+          <t>-5,88; 3,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 2,15</t>
+          <t>-7,92; 1,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 0,78</t>
+          <t>-19,75; 0,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 12,38</t>
+          <t>0,32; 12,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 10,16</t>
+          <t>-1,99; 10,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 8,96</t>
+          <t>-18,04; 8,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 13,42</t>
+          <t>0,96; 12,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 7,34</t>
+          <t>-7,66; 7,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 11,54</t>
+          <t>-5,83; 12,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,44</t>
+          <t>1,97; 11,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 6,89</t>
+          <t>-2,77; 6,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 7,88</t>
+          <t>-7,34; 8,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 14,4</t>
+          <t>0,4; 13,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 11,52</t>
+          <t>-2,08; 12,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 9,89</t>
+          <t>-19,17; 9,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 15,66</t>
+          <t>1,02; 15,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 8,24</t>
+          <t>-8,1; 8,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 13,24</t>
+          <t>-5,75; 13,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,94</t>
+          <t>2,08; 12,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 7,89</t>
+          <t>-2,97; 7,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 8,78</t>
+          <t>-7,63; 8,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 11,23</t>
+          <t>-5,51; 11,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 9,03</t>
+          <t>-8,42; 9,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-57,35; 7,15</t>
+          <t>-54,91; 7,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 4,08</t>
+          <t>-10,38; 4,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 9,11</t>
+          <t>-3,0; 7,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 2,29</t>
+          <t>-53,5; 2,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 4,22</t>
+          <t>-6,32; 4,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 5,62</t>
+          <t>-4,22; 5,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-40,86; -1,12</t>
+          <t>-38,12; -1,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 13,02</t>
+          <t>-5,55; 13,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 10,17</t>
+          <t>-8,64; 10,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 7,7</t>
+          <t>-58,96; 7,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 4,42</t>
+          <t>-10,44; 4,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 10,02</t>
+          <t>-3,0; 8,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 2,34</t>
+          <t>-54,42; 2,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 4,58</t>
+          <t>-6,36; 4,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 6,09</t>
+          <t>-4,24; 6,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,57; -1,06</t>
+          <t>-39,61; -1,11</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 11,49</t>
+          <t>-3,69; 11,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 13,74</t>
+          <t>0,11; 14,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,87; 16,24</t>
+          <t>2,83; 15,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 8,5</t>
+          <t>-5,79; 8,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 7,24</t>
+          <t>-6,93; 7,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,67</t>
+          <t>2,44; 13,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,7</t>
+          <t>-2,73; 7,92</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 8,15</t>
+          <t>-2,27; 8,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,46</t>
+          <t>3,92; 12,87</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 13,57</t>
+          <t>-3,88; 13,72</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 16,21</t>
+          <t>0,11; 17,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,03; 19,38</t>
+          <t>2,91; 18,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 9,56</t>
+          <t>-6,03; 9,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 8,0</t>
+          <t>-7,12; 8,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,49; 15,83</t>
+          <t>2,5; 16,02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 8,68</t>
+          <t>-2,85; 8,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 9,26</t>
+          <t>-2,24; 9,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,11; 14,23</t>
+          <t>4,07; 14,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 7,53</t>
+          <t>-3,92; 7,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 9,95</t>
+          <t>-1,31; 9,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-56,07; -4,6</t>
+          <t>-50,63; -5,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,09</t>
+          <t>-2,19; 7,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,05</t>
+          <t>0,37; 10,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 1,83</t>
+          <t>-23,06; 1,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,85</t>
+          <t>-2,14; 5,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,01</t>
+          <t>0,61; 8,02</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -4,48</t>
+          <t>-32,18; -4,25</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,63</t>
+          <t>-4,29; 8,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 11,45</t>
+          <t>-1,41; 11,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,03; -5,09</t>
+          <t>-55,79; -5,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,91</t>
+          <t>-2,34; 8,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,24; 11,48</t>
+          <t>0,44; 11,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 2,18</t>
+          <t>-24,52; 2,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 6,57</t>
+          <t>-2,33; 6,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,03</t>
+          <t>0,67; 9,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,79; -4,94</t>
+          <t>-35,64; -4,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 4,5</t>
+          <t>-2,85; 4,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 1,87</t>
+          <t>-6,97; 1,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 5,2</t>
+          <t>-24,57; 5,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,44</t>
+          <t>-7,19; 1,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,29; -0,7</t>
+          <t>-9,35; -0,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 4,38</t>
+          <t>-20,4; 4,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 1,58</t>
+          <t>-3,58; 1,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -0,55</t>
+          <t>-7,22; -0,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 4,1</t>
+          <t>-12,39; 3,72</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,86</t>
+          <t>-2,9; 4,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 1,97</t>
+          <t>-7,23; 1,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 5,49</t>
+          <t>-25,41; 5,84</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,53</t>
+          <t>-7,36; 1,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -0,76</t>
+          <t>-9,62; -0,55</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 4,59</t>
+          <t>-21,12; 4,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,74</t>
+          <t>-3,71; 1,71</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -0,58</t>
+          <t>-7,37; -0,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 4,28</t>
+          <t>-12,73; 3,88</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,47</t>
+          <t>-1,15; 3,27</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,89</t>
+          <t>-1,78; 2,67</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-19,39; -3,99</t>
+          <t>-20,09; -3,72</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,77</t>
+          <t>-0,57; 3,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,07</t>
+          <t>-1,09; 3,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,23</t>
+          <t>-3,54; 3,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,0</t>
+          <t>-0,01; 3,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,32</t>
+          <t>-0,86; 2,33</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,4</t>
+          <t>-8,49; -0,35</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,82</t>
+          <t>-1,21; 3,56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,16</t>
+          <t>-1,89; 2,88</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -4,32</t>
+          <t>-21,28; -3,98</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,1</t>
+          <t>-0,59; 4,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,36</t>
+          <t>-1,16; 3,57</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,58</t>
+          <t>-3,78; 4,27</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,25</t>
+          <t>-0,01; 3,39</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,5</t>
+          <t>-0,9; 2,54</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,44</t>
+          <t>-9,13; -0,38</t>
         </is>
       </c>
     </row>
